--- a/publication/figures_tables/predictors.xlsx
+++ b/publication/figures_tables/predictors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benbl\switchdrive\C.3_Modelling\LULCC_CH\publication\figures_tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bblack\switchdrive\C.3_Modelling\LULCC_CH\publication\figures_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C98253-6DDD-494C-9471-83FCDFB065E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E613A42E-1FBD-4408-84A7-FE057D22BD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="11208" xr2:uid="{9FCACA47-AF60-4148-859D-AC49C85554D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9FCACA47-AF60-4148-859D-AC49C85554D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>Distance to lakes (mean minimum dist to all lakes of different categories)</t>
   </si>
   <si>
-    <t>Distance to river (mean minimum distance (agg. From 25m data to rivers of all Strahler classes)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Average annual mean air temperature </t>
   </si>
   <si>
@@ -156,6 +153,9 @@
   </si>
   <si>
     <t>Average annual change in no. of FTE employees in the tertiary sector per labour market region</t>
+  </si>
+  <si>
+    <t>Distance to rivers (mean minimum distance, aggregated drom 25m data to rivers of all Strahler classes)</t>
   </si>
 </sst>
 </file>
@@ -541,297 +541,297 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E940F2-CADE-4487-A7C5-ABAA3ED27DCF}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.09765625" customWidth="1"/>
-    <col min="2" max="2" width="25.09765625" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="27.95" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="27.95" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="27.95" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="41.95" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="s">
+    <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="27.95" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="27.95" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="27.95" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="83.85" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="C25" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="B26" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
